--- a/Assets/Data/Excel/excel_text_talk[对话文本].xlsx
+++ b/Assets/Data/Excel/excel_text_talk[对话文本].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="TextTalk" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="287">
   <si>
     <t>id</t>
   </si>
@@ -98,10 +98,55 @@
     <t>string</t>
   </si>
   <si>
-    <t>名字</t>
+    <t>文本编号</t>
   </si>
   <si>
-    <t>内容</t>
+    <t>//类型 0默认文本 1选择对话    4书本详情  5黑幕标题  99默认</t>
+  </si>
+  <si>
+    <t>文本顺序</t>
+  </si>
+  <si>
+    <t>指定下一顺序</t>
+  </si>
+  <si>
+    <t>对话类型 0普通对话，1送礼回复对话  2招募对话  3后续对话  4第一次对话</t>
+  </si>
+  <si>
+    <t>文本发起对象ID</t>
+  </si>
+  <si>
+    <t>触发条件 好感区间</t>
+  </si>
+  <si>
+    <t>选择对话 的类型 0提示文本  1选项</t>
+  </si>
+  <si>
+    <t>增加的好感</t>
+  </si>
+  <si>
+    <t>小游戏的前置数据</t>
+  </si>
+  <si>
+    <t>奖励物品</t>
+  </si>
+  <si>
+    <t>停留时间</t>
+  </si>
+  <si>
+    <t>是否停止时间</t>
+  </si>
+  <si>
+    <t>场景人物表情</t>
+  </si>
+  <si>
+    <t>支付条件</t>
+  </si>
+  <si>
+    <t>文本发起人名字</t>
+  </si>
+  <si>
+    <t>文本内容</t>
   </si>
   <si>
     <t>AddIngVegetables:30|AddIngOilsalt:30|</t>
@@ -864,11 +909,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="10.5"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1318,19 +1362,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1339,7 +1383,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1463,9 +1507,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1818,7 +1865,7 @@
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
@@ -1958,66 +2005,66 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" ht="96.75" spans="1:20">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="T3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2758,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2911,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -2920,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S21" s="1">
         <v>1000160001003</v>
@@ -3117,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -3126,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S25" s="1">
         <v>1000160002003</v>
@@ -3323,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -3332,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S29" s="1">
         <v>1000160003003</v>
@@ -3529,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -3538,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S33" s="1">
         <v>1000160004003</v>
@@ -3735,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -3744,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="S37" s="1">
         <v>1000160005003</v>
@@ -3941,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3950,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="S41" s="1">
         <v>1000160006003</v>
@@ -5603,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="R74" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S74" s="1">
         <v>2000160001003</v>
@@ -5700,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -5859,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="R79" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="S79" s="1">
         <v>2000160002003</v>
@@ -5956,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -8015,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S122" s="1">
         <v>3000160001003</v>
@@ -8112,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -9471,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="R151" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="S151" s="1">
         <v>4000160001003</v>
@@ -9568,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -11977,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="R201" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S201" s="1">
         <v>6001160001003</v>
@@ -12074,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="N203" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -15533,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="R272" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S272" s="1">
         <v>9004100003003</v>
@@ -20680,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="N375" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="O375">
         <v>0</v>
@@ -20689,7 +20736,7 @@
         <v>0</v>
       </c>
       <c r="R375" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="S375" s="1">
         <v>10008180001002</v>
@@ -20736,7 +20783,7 @@
         <v>0</v>
       </c>
       <c r="N376" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="O376">
         <v>0</v>
@@ -20745,7 +20792,7 @@
         <v>0</v>
       </c>
       <c r="R376" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S376" s="1">
         <v>10008180001003</v>
@@ -20792,7 +20839,7 @@
         <v>0</v>
       </c>
       <c r="N377" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O377">
         <v>0</v>
@@ -20801,7 +20848,7 @@
         <v>0</v>
       </c>
       <c r="R377" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="S377" s="1">
         <v>10008180001004</v>
@@ -24248,7 +24295,7 @@
         <v>0</v>
       </c>
       <c r="N446" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="O446">
         <v>0</v>
@@ -24257,7 +24304,7 @@
         <v>0</v>
       </c>
       <c r="R446" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="S446" s="1">
         <v>11005180001002</v>
@@ -24304,7 +24351,7 @@
         <v>0</v>
       </c>
       <c r="N447" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="O447">
         <v>0</v>
@@ -24313,7 +24360,7 @@
         <v>0</v>
       </c>
       <c r="R447" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S447" s="1">
         <v>11005180001003</v>
@@ -24360,7 +24407,7 @@
         <v>0</v>
       </c>
       <c r="N448" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O448">
         <v>0</v>
@@ -24369,7 +24416,7 @@
         <v>0</v>
       </c>
       <c r="R448" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="S448" s="1">
         <v>11005180001004</v>
@@ -24416,7 +24463,7 @@
         <v>0</v>
       </c>
       <c r="N449" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="O449">
         <v>0</v>
@@ -24425,7 +24472,7 @@
         <v>0</v>
       </c>
       <c r="R449" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="S449" s="1">
         <v>11005180001005</v>
@@ -24472,7 +24519,7 @@
         <v>0</v>
       </c>
       <c r="N450" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O450">
         <v>0</v>
@@ -24481,7 +24528,7 @@
         <v>0</v>
       </c>
       <c r="R450" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="S450" s="1">
         <v>11005180001006</v>
@@ -24528,7 +24575,7 @@
         <v>0</v>
       </c>
       <c r="N451" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O451">
         <v>0</v>
@@ -24537,7 +24584,7 @@
         <v>0</v>
       </c>
       <c r="R451" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="S451" s="1">
         <v>11005180001007</v>
@@ -27590,7 +27637,7 @@
         <v>0</v>
       </c>
       <c r="R512" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S512" s="1">
         <v>21000150001004</v>
@@ -27893,7 +27940,7 @@
         <v>0</v>
       </c>
       <c r="R518" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S518" s="1">
         <v>21000150002003</v>
@@ -27946,7 +27993,7 @@
         <v>0</v>
       </c>
       <c r="R519" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S519" s="1">
         <v>21000150002004</v>
@@ -28299,7 +28346,7 @@
         <v>0</v>
       </c>
       <c r="R526" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S526" s="1">
         <v>21000150003003</v>
@@ -28652,7 +28699,7 @@
         <v>0</v>
       </c>
       <c r="R533" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="S533" s="1">
         <v>21000150004004</v>
@@ -28705,7 +28752,7 @@
         <v>0</v>
       </c>
       <c r="R534" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="S534" s="1">
         <v>21000150004005</v>
@@ -29058,7 +29105,7 @@
         <v>0</v>
       </c>
       <c r="R541" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="S541" s="1">
         <v>21000150005003</v>
@@ -30061,7 +30108,7 @@
         <v>0</v>
       </c>
       <c r="R561" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="S561" s="1">
         <v>21000250001004</v>
@@ -30114,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="R562" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S562" s="1">
         <v>21000250001005</v>
@@ -30467,7 +30514,7 @@
         <v>0</v>
       </c>
       <c r="R569" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="S569" s="1">
         <v>21000250002003</v>
@@ -30520,7 +30567,7 @@
         <v>0</v>
       </c>
       <c r="R570" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S570" s="1">
         <v>21000250002004</v>
@@ -30873,7 +30920,7 @@
         <v>0</v>
       </c>
       <c r="R577" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="S577" s="1">
         <v>21000250003003</v>
@@ -30926,7 +30973,7 @@
         <v>0</v>
       </c>
       <c r="R578" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="S578" s="1">
         <v>21000250003004</v>
@@ -31279,7 +31326,7 @@
         <v>0</v>
       </c>
       <c r="R585" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S585" s="1">
         <v>21000250004003</v>
@@ -31332,7 +31379,7 @@
         <v>0</v>
       </c>
       <c r="R586" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="S586" s="1">
         <v>21000250004004</v>
@@ -31685,7 +31732,7 @@
         <v>0</v>
       </c>
       <c r="R593" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="S593" s="1">
         <v>21000250005003</v>
@@ -31782,7 +31829,7 @@
         <v>1</v>
       </c>
       <c r="N595" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="O595">
         <v>0</v>
@@ -32091,7 +32138,7 @@
         <v>0</v>
       </c>
       <c r="R601" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S601" s="1">
         <v>21000350001005</v>
@@ -32444,7 +32491,7 @@
         <v>0</v>
       </c>
       <c r="R608" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S608" s="1">
         <v>21000350002003</v>
@@ -32797,7 +32844,7 @@
         <v>0</v>
       </c>
       <c r="R615" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="S615" s="1">
         <v>21000350003004</v>
@@ -33150,7 +33197,7 @@
         <v>0</v>
       </c>
       <c r="R622" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="S622" s="1">
         <v>21000350004003</v>
@@ -33203,7 +33250,7 @@
         <v>0</v>
       </c>
       <c r="R623" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="S623" s="1">
         <v>21000350004004</v>
@@ -33556,7 +33603,7 @@
         <v>0</v>
       </c>
       <c r="R630" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="S630" s="1">
         <v>21000350005003</v>
@@ -34003,7 +34050,7 @@
         <v>0</v>
       </c>
       <c r="N639" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="O639">
         <v>0</v>
@@ -34012,7 +34059,7 @@
         <v>0</v>
       </c>
       <c r="R639" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S639" s="1">
         <v>30001120001004</v>
@@ -34909,7 +34956,7 @@
         <v>0</v>
       </c>
       <c r="N657" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="O657">
         <v>0</v>
@@ -35412,7 +35459,7 @@
         <v>0</v>
       </c>
       <c r="N667" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="O667">
         <v>0</v>
@@ -35421,7 +35468,7 @@
         <v>0</v>
       </c>
       <c r="R667" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="S667" s="1">
         <v>30003120001004</v>
@@ -35818,10 +35865,10 @@
         <v>0</v>
       </c>
       <c r="M675" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="N675" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="O675">
         <v>0</v>
@@ -36324,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="M685" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="N685" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="O685">
         <v>0</v>
@@ -36880,10 +36927,10 @@
         <v>0</v>
       </c>
       <c r="M696" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="N696" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="O696">
         <v>0</v>
@@ -37392,7 +37439,7 @@
         <v>0</v>
       </c>
       <c r="R706" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="S706" s="1">
         <v>31001120001004</v>
@@ -37489,7 +37536,7 @@
         <v>0</v>
       </c>
       <c r="N708" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="O708">
         <v>0</v>
@@ -37848,7 +37895,7 @@
         <v>0</v>
       </c>
       <c r="R715" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="S715" s="1">
         <v>31002120001004</v>
@@ -37945,7 +37992,7 @@
         <v>0</v>
       </c>
       <c r="N717" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="O717">
         <v>0</v>
@@ -38848,7 +38895,7 @@
         <v>0</v>
       </c>
       <c r="N735" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="O735">
         <v>0</v>
@@ -39307,7 +39354,7 @@
         <v>0</v>
       </c>
       <c r="R744" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="S744" s="1">
         <v>31004120001005</v>
@@ -39404,7 +39451,7 @@
         <v>0</v>
       </c>
       <c r="N746" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="O746">
         <v>0</v>
@@ -39763,7 +39810,7 @@
         <v>0</v>
       </c>
       <c r="R753" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="S753" s="1">
         <v>31005120001004</v>
@@ -39860,7 +39907,7 @@
         <v>0</v>
       </c>
       <c r="N755" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="O755">
         <v>0</v>
@@ -40319,7 +40366,7 @@
         <v>0</v>
       </c>
       <c r="R764" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="S764" s="1">
         <v>31006120001005</v>
@@ -40416,7 +40463,7 @@
         <v>0</v>
       </c>
       <c r="N766" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="O766">
         <v>0</v>
@@ -40975,7 +41022,7 @@
         <v>0</v>
       </c>
       <c r="R777" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="S777" s="1">
         <v>32000120001007</v>
@@ -41072,7 +41119,7 @@
         <v>0</v>
       </c>
       <c r="N779" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="O779">
         <v>0</v>
@@ -41575,7 +41622,7 @@
         <v>0</v>
       </c>
       <c r="N789" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="O789">
         <v>0</v>
@@ -42078,7 +42125,7 @@
         <v>0</v>
       </c>
       <c r="N799" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="O799">
         <v>0</v>
@@ -42331,7 +42378,7 @@
         <v>0</v>
       </c>
       <c r="M804" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="O804">
         <v>0</v>
@@ -42484,7 +42531,7 @@
         <v>0</v>
       </c>
       <c r="N807" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="O807">
         <v>0</v>
@@ -42793,7 +42840,7 @@
         <v>0</v>
       </c>
       <c r="R813" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S813" s="1">
         <v>32004120001004</v>
@@ -42890,7 +42937,7 @@
         <v>0</v>
       </c>
       <c r="N815" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="O815">
         <v>0</v>
@@ -43299,7 +43346,7 @@
         <v>0</v>
       </c>
       <c r="R823" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="S823" s="1">
         <v>32005120001005</v>
@@ -43396,7 +43443,7 @@
         <v>0</v>
       </c>
       <c r="N825" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O825">
         <v>0</v>
@@ -43555,7 +43602,7 @@
         <v>0</v>
       </c>
       <c r="R828" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S828" s="1">
         <v>40000160001003</v>
@@ -43608,7 +43655,7 @@
         <v>0</v>
       </c>
       <c r="R829" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S829" s="1">
         <v>40000160001004</v>
@@ -43661,7 +43708,7 @@
         <v>0</v>
       </c>
       <c r="R830" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="S830" s="1">
         <v>40000160001005</v>
@@ -43958,7 +44005,7 @@
         <v>0</v>
       </c>
       <c r="N836" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O836">
         <v>0</v>
@@ -44167,7 +44214,7 @@
         <v>0</v>
       </c>
       <c r="R840" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="S840" s="1">
         <v>40000260001003</v>
@@ -44420,7 +44467,7 @@
         <v>0</v>
       </c>
       <c r="R845" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="S845" s="1">
         <v>40000260002003</v>
@@ -44473,7 +44520,7 @@
         <v>0</v>
       </c>
       <c r="R846" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="S846" s="1">
         <v>40000260002004</v>
@@ -44770,7 +44817,7 @@
         <v>0</v>
       </c>
       <c r="N852" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="O852">
         <v>0</v>
@@ -44923,7 +44970,7 @@
         <v>0</v>
       </c>
       <c r="N855" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="O855">
         <v>0</v>
@@ -44932,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="R855" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="S855" s="1">
         <v>40000560001003</v>
@@ -44985,7 +45032,7 @@
         <v>0</v>
       </c>
       <c r="R856" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="S856" s="1">
         <v>40000560001004</v>
@@ -45282,7 +45329,7 @@
         <v>0</v>
       </c>
       <c r="N862" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="O862">
         <v>0</v>
@@ -45291,7 +45338,7 @@
         <v>0</v>
       </c>
       <c r="R862" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="S862" s="1">
         <v>40000560002003</v>
@@ -45344,7 +45391,7 @@
         <v>0</v>
       </c>
       <c r="R863" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="S863" s="1">
         <v>40000560002004</v>
@@ -45691,7 +45738,7 @@
         <v>0</v>
       </c>
       <c r="N870" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="O870">
         <v>0</v>
@@ -45900,7 +45947,7 @@
         <v>0</v>
       </c>
       <c r="R874" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="S874" s="1">
         <v>40000660001003</v>
@@ -45953,7 +46000,7 @@
         <v>0</v>
       </c>
       <c r="R875" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="S875" s="1">
         <v>40000660001004</v>
@@ -46300,7 +46347,7 @@
         <v>0</v>
       </c>
       <c r="N882" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O882">
         <v>0</v>
@@ -46559,7 +46606,7 @@
         <v>0</v>
       </c>
       <c r="R887" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="S887" s="1">
         <v>40000760001003</v>
@@ -46812,7 +46859,7 @@
         <v>0</v>
       </c>
       <c r="R892" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S892" s="1">
         <v>40000760002003</v>
@@ -47065,7 +47112,7 @@
         <v>0</v>
       </c>
       <c r="R897" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S897" s="1">
         <v>40000760003003</v>
@@ -47118,7 +47165,7 @@
         <v>0</v>
       </c>
       <c r="R898" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="S898" s="1">
         <v>40000760003004</v>
@@ -47365,7 +47412,7 @@
         <v>0</v>
       </c>
       <c r="N903" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="O903">
         <v>0</v>
@@ -47524,7 +47571,7 @@
         <v>0</v>
       </c>
       <c r="R906" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S906" s="1">
         <v>40100160001003</v>
@@ -48077,7 +48124,7 @@
         <v>0</v>
       </c>
       <c r="R917" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S917" s="1">
         <v>40100360001004</v>
@@ -48674,7 +48721,7 @@
         <v>0</v>
       </c>
       <c r="N929" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O929">
         <v>0</v>
@@ -48683,7 +48730,7 @@
         <v>0</v>
       </c>
       <c r="R929" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S929" s="1">
         <v>40100460001003</v>
@@ -48730,7 +48777,7 @@
         <v>0</v>
       </c>
       <c r="N930" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="O930">
         <v>0</v>
@@ -48739,7 +48786,7 @@
         <v>0</v>
       </c>
       <c r="R930" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S930" s="1">
         <v>40100460001004</v>
@@ -48992,7 +49039,7 @@
         <v>0</v>
       </c>
       <c r="R935" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="S935" s="1">
         <v>40100560001003</v>
@@ -49289,7 +49336,7 @@
         <v>0</v>
       </c>
       <c r="N941" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="O941">
         <v>0</v>
@@ -49298,7 +49345,7 @@
         <v>0</v>
       </c>
       <c r="R941" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S941" s="1">
         <v>40100560002003</v>
@@ -49345,7 +49392,7 @@
         <v>0</v>
       </c>
       <c r="N942" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="O942">
         <v>0</v>
@@ -49354,7 +49401,7 @@
         <v>0</v>
       </c>
       <c r="R942" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="S942" s="1">
         <v>40100560002004</v>
@@ -49601,7 +49648,7 @@
         <v>0</v>
       </c>
       <c r="N947" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O947">
         <v>0</v>
@@ -49754,7 +49801,7 @@
         <v>0</v>
       </c>
       <c r="N950" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O950">
         <v>0</v>
@@ -49763,7 +49810,7 @@
         <v>0</v>
       </c>
       <c r="R950" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S950" s="1">
         <v>40100660001003</v>
@@ -50266,7 +50313,7 @@
         <v>0</v>
       </c>
       <c r="R960" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="S960" s="1">
         <v>40200160002003</v>
@@ -50819,7 +50866,7 @@
         <v>0</v>
       </c>
       <c r="R971" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S971" s="1">
         <v>40200260001003</v>
@@ -51222,7 +51269,7 @@
         <v>0</v>
       </c>
       <c r="R979" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S979" s="1">
         <v>40200360001003</v>
@@ -51569,7 +51616,7 @@
         <v>0</v>
       </c>
       <c r="N986" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="O986">
         <v>0</v>
@@ -51578,7 +51625,7 @@
         <v>0</v>
       </c>
       <c r="R986" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="S986" s="1">
         <v>40200560001003</v>
@@ -51831,7 +51878,7 @@
         <v>0</v>
       </c>
       <c r="R991" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="S991" s="1">
         <v>40200660001003</v>
@@ -51884,7 +51931,7 @@
         <v>0</v>
       </c>
       <c r="R992" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="S992" s="1">
         <v>40200660001004</v>
@@ -52337,7 +52384,7 @@
         <v>0</v>
       </c>
       <c r="R1001" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="S1001" s="1">
         <v>40200660002006</v>
@@ -52390,7 +52437,7 @@
         <v>0</v>
       </c>
       <c r="R1002" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="S1002" s="1">
         <v>40200660002007</v>
@@ -52537,7 +52584,7 @@
         <v>-1</v>
       </c>
       <c r="N1005" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="O1005">
         <v>0</v>
@@ -52740,7 +52787,7 @@
         <v>0</v>
       </c>
       <c r="N1009" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="O1009">
         <v>0</v>
@@ -52943,7 +52990,7 @@
         <v>0</v>
       </c>
       <c r="N1013" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="O1013">
         <v>0</v>
@@ -52952,7 +52999,7 @@
         <v>0</v>
       </c>
       <c r="R1013" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S1013" s="1">
         <v>40300160001003</v>
@@ -53205,7 +53252,7 @@
         <v>0</v>
       </c>
       <c r="R1018" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="S1018" s="1">
         <v>40300160002003</v>
@@ -53258,7 +53305,7 @@
         <v>0</v>
       </c>
       <c r="R1019" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S1019" s="1">
         <v>40300160002004</v>
@@ -55705,7 +55752,7 @@
         <v>0</v>
       </c>
       <c r="N1068" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="O1068">
         <v>0</v>
@@ -56314,7 +56361,7 @@
         <v>0</v>
       </c>
       <c r="R1080" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="S1080" s="1">
         <v>40400160001003</v>
@@ -57061,7 +57108,7 @@
         <v>0</v>
       </c>
       <c r="N1095" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="O1095">
         <v>0</v>
@@ -57070,7 +57117,7 @@
         <v>0</v>
       </c>
       <c r="R1095" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="S1095" s="1">
         <v>40400460001003</v>
@@ -57117,7 +57164,7 @@
         <v>0</v>
       </c>
       <c r="N1096" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="O1096">
         <v>0</v>
@@ -57126,7 +57173,7 @@
         <v>0</v>
       </c>
       <c r="R1096" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="S1096" s="1">
         <v>40400460001004</v>
@@ -57423,7 +57470,7 @@
         <v>0</v>
       </c>
       <c r="N1102" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="O1102">
         <v>0</v>
@@ -57432,7 +57479,7 @@
         <v>0</v>
       </c>
       <c r="R1102" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="S1102" s="1">
         <v>40400560001003</v>
@@ -57685,7 +57732,7 @@
         <v>0</v>
       </c>
       <c r="R1107" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="S1107" s="1">
         <v>40500260001003</v>
@@ -57738,7 +57785,7 @@
         <v>0</v>
       </c>
       <c r="R1108" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="S1108" s="1">
         <v>40500260001004</v>
@@ -58041,7 +58088,7 @@
         <v>0</v>
       </c>
       <c r="R1114" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="S1114" s="1">
         <v>40500360001003</v>
@@ -58294,7 +58341,7 @@
         <v>0</v>
       </c>
       <c r="R1119" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="S1119" s="1">
         <v>40500460001003</v>
@@ -58597,7 +58644,7 @@
         <v>0</v>
       </c>
       <c r="R1125" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S1125" s="1">
         <v>40500660001003</v>
@@ -59244,7 +59291,7 @@
         <v>0</v>
       </c>
       <c r="N1138" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="O1138">
         <v>0</v>
@@ -59253,7 +59300,7 @@
         <v>0</v>
       </c>
       <c r="R1138" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="S1138" s="1">
         <v>41100160001003</v>
@@ -59300,7 +59347,7 @@
         <v>0</v>
       </c>
       <c r="N1139" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="O1139">
         <v>0</v>
@@ -59309,7 +59356,7 @@
         <v>0</v>
       </c>
       <c r="R1139" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="S1139" s="1">
         <v>41100160001004</v>
@@ -59756,7 +59803,7 @@
         <v>0</v>
       </c>
       <c r="N1148" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="O1148">
         <v>0</v>
@@ -59765,7 +59812,7 @@
         <v>0</v>
       </c>
       <c r="R1148" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="S1148" s="1">
         <v>50000180001003</v>
@@ -59812,7 +59859,7 @@
         <v>0</v>
       </c>
       <c r="N1149" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="O1149">
         <v>0</v>
@@ -59821,7 +59868,7 @@
         <v>0</v>
       </c>
       <c r="R1149" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="S1149" s="1">
         <v>50000180001004</v>
@@ -59868,7 +59915,7 @@
         <v>0</v>
       </c>
       <c r="N1150" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="O1150">
         <v>0</v>
@@ -59877,7 +59924,7 @@
         <v>0</v>
       </c>
       <c r="R1150" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="S1150" s="1">
         <v>50000180001005</v>
@@ -59924,7 +59971,7 @@
         <v>0</v>
       </c>
       <c r="N1151" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="O1151">
         <v>0</v>
@@ -59933,7 +59980,7 @@
         <v>0</v>
       </c>
       <c r="R1151" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="S1151" s="1">
         <v>50000180001006</v>
@@ -59980,7 +60027,7 @@
         <v>0</v>
       </c>
       <c r="N1152" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="O1152">
         <v>0</v>
@@ -59989,7 +60036,7 @@
         <v>0</v>
       </c>
       <c r="R1152" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="S1152" s="1">
         <v>50000180001007</v>
@@ -60036,7 +60083,7 @@
         <v>0</v>
       </c>
       <c r="N1153" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="O1153">
         <v>0</v>
@@ -60045,7 +60092,7 @@
         <v>0</v>
       </c>
       <c r="R1153" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="S1153" s="1">
         <v>50000180001008</v>
@@ -60092,7 +60139,7 @@
         <v>0</v>
       </c>
       <c r="N1154" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="O1154">
         <v>0</v>
@@ -60101,7 +60148,7 @@
         <v>0</v>
       </c>
       <c r="R1154" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="S1154" s="1">
         <v>50000180001009</v>
@@ -60148,7 +60195,7 @@
         <v>0</v>
       </c>
       <c r="N1155" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="O1155">
         <v>0</v>
@@ -60157,7 +60204,7 @@
         <v>0</v>
       </c>
       <c r="R1155" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="S1155" s="1">
         <v>50000180001010</v>
@@ -60204,7 +60251,7 @@
         <v>0</v>
       </c>
       <c r="N1156" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="O1156">
         <v>0</v>
@@ -60213,7 +60260,7 @@
         <v>0</v>
       </c>
       <c r="R1156" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="S1156" s="1">
         <v>50000180001011</v>
@@ -60260,7 +60307,7 @@
         <v>0</v>
       </c>
       <c r="N1157" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="O1157">
         <v>0</v>
@@ -60269,7 +60316,7 @@
         <v>0</v>
       </c>
       <c r="R1157" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="S1157" s="1">
         <v>50000180001012</v>
@@ -60316,7 +60363,7 @@
         <v>1</v>
       </c>
       <c r="N1158" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="O1158">
         <v>0</v>
@@ -60325,7 +60372,7 @@
         <v>0</v>
       </c>
       <c r="R1158" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="S1158" s="1">
         <v>50000180001013</v>
@@ -60372,7 +60419,7 @@
         <v>1</v>
       </c>
       <c r="N1159" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="O1159">
         <v>0</v>
@@ -60381,7 +60428,7 @@
         <v>0</v>
       </c>
       <c r="R1159" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="S1159" s="1">
         <v>50000180001014</v>
@@ -60678,7 +60725,7 @@
         <v>0</v>
       </c>
       <c r="N1165" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="O1165">
         <v>0</v>
@@ -60687,7 +60734,7 @@
         <v>0</v>
       </c>
       <c r="R1165" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="S1165" s="1">
         <v>50000280001003</v>
@@ -60734,7 +60781,7 @@
         <v>0</v>
       </c>
       <c r="N1166" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="O1166">
         <v>0</v>
@@ -60743,7 +60790,7 @@
         <v>0</v>
       </c>
       <c r="R1166" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="S1166" s="1">
         <v>50000280001004</v>
@@ -60790,7 +60837,7 @@
         <v>0</v>
       </c>
       <c r="N1167" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="O1167">
         <v>0</v>
@@ -60799,7 +60846,7 @@
         <v>0</v>
       </c>
       <c r="R1167" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="S1167" s="1">
         <v>50000280001005</v>
@@ -60846,7 +60893,7 @@
         <v>0</v>
       </c>
       <c r="N1168" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="O1168">
         <v>0</v>
@@ -60855,7 +60902,7 @@
         <v>0</v>
       </c>
       <c r="R1168" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="S1168" s="1">
         <v>50000280001006</v>
@@ -60902,7 +60949,7 @@
         <v>0</v>
       </c>
       <c r="N1169" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="O1169">
         <v>0</v>
@@ -60911,7 +60958,7 @@
         <v>0</v>
       </c>
       <c r="R1169" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="S1169" s="1">
         <v>50000280001007</v>
@@ -61258,7 +61305,7 @@
         <v>0</v>
       </c>
       <c r="N1176" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O1176">
         <v>0</v>
@@ -61567,7 +61614,7 @@
         <v>0</v>
       </c>
       <c r="R1182" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="S1182" s="1">
         <v>90000200001004</v>
@@ -61620,7 +61667,7 @@
         <v>0</v>
       </c>
       <c r="R1183" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="S1183" s="1">
         <v>90000200001005</v>
@@ -61967,7 +62014,7 @@
         <v>0</v>
       </c>
       <c r="N1190" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O1190">
         <v>0</v>
@@ -62126,7 +62173,7 @@
         <v>0</v>
       </c>
       <c r="R1193" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S1193" s="1">
         <v>90001100001003</v>
@@ -62179,7 +62226,7 @@
         <v>0</v>
       </c>
       <c r="R1194" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S1194" s="1">
         <v>90001100001004</v>
@@ -62526,7 +62573,7 @@
         <v>0</v>
       </c>
       <c r="N1201" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O1201">
         <v>0</v>
@@ -62535,7 +62582,7 @@
         <v>0</v>
       </c>
       <c r="R1201" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S1201" s="1">
         <v>90001200001004</v>
@@ -62832,7 +62879,7 @@
         <v>0</v>
       </c>
       <c r="N1207" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="O1207">
         <v>0</v>
@@ -63385,7 +63432,7 @@
         <v>0</v>
       </c>
       <c r="N1218" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="O1218">
         <v>0</v>
@@ -63644,7 +63691,7 @@
         <v>0</v>
       </c>
       <c r="R1223" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="S1223" s="1">
         <v>90004100001005</v>
@@ -63741,7 +63788,7 @@
         <v>0</v>
       </c>
       <c r="N1225" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="O1225">
         <v>0</v>
@@ -64044,7 +64091,7 @@
         <v>0</v>
       </c>
       <c r="M1231" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="O1231">
         <v>0</v>
@@ -64197,7 +64244,7 @@
         <v>0</v>
       </c>
       <c r="N1234" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="O1234">
         <v>0</v>
@@ -64506,7 +64553,7 @@
         <v>0</v>
       </c>
       <c r="R1240" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="S1240" s="1">
         <v>90006100001005</v>
@@ -64653,7 +64700,7 @@
         <v>0</v>
       </c>
       <c r="N1243" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O1243">
         <v>0</v>
@@ -65606,7 +65653,7 @@
         <v>0</v>
       </c>
       <c r="N1262" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="O1262">
         <v>0</v>
@@ -66315,7 +66362,7 @@
         <v>0</v>
       </c>
       <c r="R1276" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="S1276" s="1">
         <v>91000100001005</v>
@@ -66412,7 +66459,7 @@
         <v>0</v>
       </c>
       <c r="N1278" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="O1278">
         <v>0</v>
@@ -66771,7 +66818,7 @@
         <v>0</v>
       </c>
       <c r="R1285" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="S1285" s="1">
         <v>91001100001006</v>
@@ -66868,7 +66915,7 @@
         <v>0</v>
       </c>
       <c r="N1287" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="O1287">
         <v>0</v>
@@ -67077,7 +67124,7 @@
         <v>0</v>
       </c>
       <c r="R1291" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="S1291" s="1">
         <v>91002100001004</v>
@@ -67224,7 +67271,7 @@
         <v>0</v>
       </c>
       <c r="N1294" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="O1294">
         <v>0</v>
@@ -67427,7 +67474,7 @@
         <v>0</v>
       </c>
       <c r="M1298" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="O1298">
         <v>0</v>
@@ -67580,7 +67627,7 @@
         <v>0</v>
       </c>
       <c r="N1301" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="O1301">
         <v>0</v>
@@ -67989,7 +68036,7 @@
         <v>0</v>
       </c>
       <c r="R1309" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="S1309" s="1">
         <v>91004100001007</v>
@@ -68086,7 +68133,7 @@
         <v>0</v>
       </c>
       <c r="N1311" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="O1311">
         <v>0</v>
@@ -68339,7 +68386,7 @@
         <v>0</v>
       </c>
       <c r="N1316" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="O1316">
         <v>0</v>
@@ -68642,7 +68689,7 @@
         <v>0</v>
       </c>
       <c r="M1322" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="O1322">
         <v>0</v>
@@ -68795,7 +68842,7 @@
         <v>0</v>
       </c>
       <c r="N1325" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="O1325">
         <v>0</v>
@@ -69148,7 +69195,7 @@
         <v>0</v>
       </c>
       <c r="M1332" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="O1332">
         <v>0</v>
@@ -69301,7 +69348,7 @@
         <v>0</v>
       </c>
       <c r="N1335" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="O1335">
         <v>0</v>
@@ -69610,7 +69657,7 @@
         <v>0</v>
       </c>
       <c r="R1341" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="S1341" s="1">
         <v>91008100001005</v>
@@ -69707,7 +69754,7 @@
         <v>0</v>
       </c>
       <c r="N1343" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O1343">
         <v>0</v>
@@ -70116,7 +70163,7 @@
         <v>0</v>
       </c>
       <c r="R1351" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="S1351" s="1">
         <v>91009100001006</v>
@@ -70213,7 +70260,7 @@
         <v>0</v>
       </c>
       <c r="N1353" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="O1353">
         <v>0</v>
@@ -70466,7 +70513,7 @@
         <v>0</v>
       </c>
       <c r="M1358" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="O1358">
         <v>0</v>
@@ -70669,7 +70716,7 @@
         <v>0</v>
       </c>
       <c r="N1362" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="O1362">
         <v>0</v>
@@ -70978,7 +71025,7 @@
         <v>0</v>
       </c>
       <c r="R1368" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="S1368" s="1">
         <v>91011100001006</v>
@@ -71175,7 +71222,7 @@
         <v>0</v>
       </c>
       <c r="N1372" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="O1372">
         <v>0</v>
@@ -71678,7 +71725,7 @@
         <v>0</v>
       </c>
       <c r="N1382" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="O1382">
         <v>0</v>
@@ -72137,7 +72184,7 @@
         <v>0</v>
       </c>
       <c r="R1391" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="S1391" s="1">
         <v>91013100001008</v>
@@ -72334,7 +72381,7 @@
         <v>0</v>
       </c>
       <c r="N1395" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="O1395">
         <v>0</v>
@@ -72487,10 +72534,10 @@
         <v>0</v>
       </c>
       <c r="M1398" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="N1398" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="O1398">
         <v>0</v>
@@ -72543,10 +72590,10 @@
         <v>0</v>
       </c>
       <c r="M1399" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="N1399" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="O1399">
         <v>0</v>
@@ -72599,10 +72646,10 @@
         <v>0</v>
       </c>
       <c r="M1400" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N1400" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="O1400">
         <v>0</v>
@@ -72655,10 +72702,10 @@
         <v>0</v>
       </c>
       <c r="M1401" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="N1401" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="O1401">
         <v>0</v>
@@ -72711,10 +72758,10 @@
         <v>0</v>
       </c>
       <c r="M1402" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="N1402" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="O1402">
         <v>0</v>
@@ -72767,10 +72814,10 @@
         <v>0</v>
       </c>
       <c r="M1403" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="N1403" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="O1403">
         <v>0</v>
@@ -72823,10 +72870,10 @@
         <v>0</v>
       </c>
       <c r="M1404" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="N1404" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="O1404">
         <v>0</v>
@@ -72879,10 +72926,10 @@
         <v>0</v>
       </c>
       <c r="M1405" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="N1405" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="O1405">
         <v>0</v>
@@ -72935,10 +72982,10 @@
         <v>0</v>
       </c>
       <c r="M1406" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="N1406" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="O1406">
         <v>0</v>
@@ -73091,7 +73138,7 @@
         <v>0</v>
       </c>
       <c r="N1409" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="O1409">
         <v>0</v>
@@ -74094,7 +74141,7 @@
         <v>0</v>
       </c>
       <c r="N1429" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="O1429">
         <v>0</v>
@@ -74303,7 +74350,7 @@
         <v>0</v>
       </c>
       <c r="R1433" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="S1433" s="1">
         <v>92002100001004</v>
@@ -74656,7 +74703,7 @@
         <v>0</v>
       </c>
       <c r="R1440" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S1440" s="1">
         <v>92003100001005</v>
@@ -75203,7 +75250,7 @@
         <v>0</v>
       </c>
       <c r="M1451" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="O1451">
         <v>0</v>
@@ -75406,7 +75453,7 @@
         <v>0</v>
       </c>
       <c r="N1455" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="O1455">
         <v>0</v>
@@ -75759,7 +75806,7 @@
         <v>0</v>
       </c>
       <c r="M1462" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="O1462">
         <v>0</v>
@@ -75862,7 +75909,7 @@
         <v>0</v>
       </c>
       <c r="N1464" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="O1464">
         <v>0</v>
@@ -76165,7 +76212,7 @@
         <v>0</v>
       </c>
       <c r="M1470" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="O1470">
         <v>0</v>
@@ -76318,7 +76365,7 @@
         <v>0</v>
       </c>
       <c r="N1473" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="O1473">
         <v>0</v>
@@ -76677,7 +76724,7 @@
         <v>0</v>
       </c>
       <c r="R1480" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="S1480" s="1">
         <v>92007100001006</v>
@@ -76874,7 +76921,7 @@
         <v>0</v>
       </c>
       <c r="N1484" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="O1484">
         <v>0</v>
@@ -77127,7 +77174,7 @@
         <v>0</v>
       </c>
       <c r="M1489" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="O1489">
         <v>0</v>
@@ -77330,7 +77377,7 @@
         <v>0</v>
       </c>
       <c r="N1493" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="O1493">
         <v>0</v>
@@ -77633,7 +77680,7 @@
         <v>0</v>
       </c>
       <c r="M1499" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="O1499">
         <v>0</v>
@@ -77786,7 +77833,7 @@
         <v>0</v>
       </c>
       <c r="N1502" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="O1502">
         <v>0</v>
@@ -78039,7 +78086,7 @@
         <v>0</v>
       </c>
       <c r="M1507" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="O1507">
         <v>0</v>
@@ -78242,7 +78289,7 @@
         <v>0</v>
       </c>
       <c r="N1511" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="O1511">
         <v>0</v>
@@ -78551,7 +78598,7 @@
         <v>0</v>
       </c>
       <c r="R1517" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="S1517" s="1">
         <v>92011100001005</v>
@@ -78604,7 +78651,7 @@
         <v>0</v>
       </c>
       <c r="R1518" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="S1518" s="1">
         <v>92011100001006</v>
@@ -78657,7 +78704,7 @@
         <v>0</v>
       </c>
       <c r="R1519" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="S1519" s="1">
         <v>92011100001007</v>
@@ -78710,7 +78757,7 @@
         <v>0</v>
       </c>
       <c r="R1520" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="S1520" s="1">
         <v>92011100001008</v>
@@ -78763,7 +78810,7 @@
         <v>0</v>
       </c>
       <c r="R1521" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="S1521" s="1">
         <v>92011100001009</v>
@@ -78910,7 +78957,7 @@
         <v>0</v>
       </c>
       <c r="N1524" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="O1524">
         <v>0</v>
@@ -79263,7 +79310,7 @@
         <v>0</v>
       </c>
       <c r="M1531" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="O1531">
         <v>0</v>
@@ -79516,7 +79563,7 @@
         <v>0</v>
       </c>
       <c r="N1536" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="O1536">
         <v>0</v>
@@ -79825,7 +79872,7 @@
         <v>0</v>
       </c>
       <c r="R1542" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="S1542" s="1">
         <v>92013100001005</v>
@@ -80072,7 +80119,7 @@
         <v>0</v>
       </c>
       <c r="N1547" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="O1547">
         <v>0</v>
@@ -80381,7 +80428,7 @@
         <v>0</v>
       </c>
       <c r="R1553" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="S1553" s="1">
         <v>92014100001006</v>
@@ -80628,7 +80675,7 @@
         <v>0</v>
       </c>
       <c r="N1558" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="O1558">
         <v>0</v>
@@ -80881,7 +80928,7 @@
         <v>0</v>
       </c>
       <c r="M1563" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="O1563">
         <v>0</v>
@@ -81084,7 +81131,7 @@
         <v>0</v>
       </c>
       <c r="N1567" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="O1567">
         <v>0</v>
@@ -81443,7 +81490,7 @@
         <v>0</v>
       </c>
       <c r="R1574" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="S1574" s="1">
         <v>92016100001006</v>
@@ -81496,7 +81543,7 @@
         <v>0</v>
       </c>
       <c r="R1575" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S1575" s="1">
         <v>92016100001007</v>
@@ -81549,7 +81596,7 @@
         <v>0</v>
       </c>
       <c r="R1576" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="S1576" s="1">
         <v>92016100001008</v>
@@ -81746,7 +81793,7 @@
         <v>0</v>
       </c>
       <c r="N1580" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="O1580">
         <v>0</v>
@@ -82699,7 +82746,7 @@
         <v>0</v>
       </c>
       <c r="N1599" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="O1599">
         <v>0</v>
@@ -82958,7 +83005,7 @@
         <v>0</v>
       </c>
       <c r="R1604" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="S1604" s="1">
         <v>92018100001005</v>
@@ -83105,7 +83152,7 @@
         <v>0</v>
       </c>
       <c r="N1607" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="O1607">
         <v>0</v>
@@ -83608,7 +83655,7 @@
         <v>0</v>
       </c>
       <c r="N1617" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="O1617">
         <v>0</v>
@@ -83811,7 +83858,7 @@
         <v>0</v>
       </c>
       <c r="N1621" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="O1621">
         <v>0</v>
@@ -84014,7 +84061,7 @@
         <v>0</v>
       </c>
       <c r="N1625" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="O1625">
         <v>0</v>
@@ -84217,7 +84264,7 @@
         <v>0</v>
       </c>
       <c r="N1629" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="O1629">
         <v>0</v>
@@ -84870,7 +84917,7 @@
         <v>0</v>
       </c>
       <c r="N1642" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="O1642">
         <v>0</v>
@@ -85179,7 +85226,7 @@
         <v>0</v>
       </c>
       <c r="R1648" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="S1648" s="1">
         <v>92024100001006</v>
@@ -85326,7 +85373,7 @@
         <v>0</v>
       </c>
       <c r="N1651" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="O1651">
         <v>0</v>
@@ -85529,7 +85576,7 @@
         <v>0</v>
       </c>
       <c r="N1655" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="O1655">
         <v>0</v>
@@ -85538,7 +85585,7 @@
         <v>0</v>
       </c>
       <c r="R1655" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="S1655" s="1">
         <v>92025100001003</v>
@@ -85735,7 +85782,7 @@
         <v>0</v>
       </c>
       <c r="N1659" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="O1659">
         <v>0</v>
@@ -85744,7 +85791,7 @@
         <v>0</v>
       </c>
       <c r="R1659" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="S1659" s="1">
         <v>92025180001002</v>
@@ -85791,7 +85838,7 @@
         <v>0</v>
       </c>
       <c r="N1660" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="O1660">
         <v>0</v>
@@ -85800,7 +85847,7 @@
         <v>0</v>
       </c>
       <c r="R1660" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S1660" s="1">
         <v>92025180001003</v>
@@ -85847,7 +85894,7 @@
         <v>0</v>
       </c>
       <c r="N1661" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="O1661">
         <v>0</v>
@@ -85856,7 +85903,7 @@
         <v>0</v>
       </c>
       <c r="R1661" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="S1661" s="1">
         <v>92025180001004</v>
